--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512637_ELIMINGRB14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512637_ELIMINGRB14FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9597</v>
+        <v>4.2331</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7505</v>
+        <v>6.5887</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7907</v>
+        <v>-2.3556</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6432</v>
+        <v>1.574</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.2189</v>
+        <v>-1.3081</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8621</v>
+        <v>2.8821</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5667</v>
+        <v>4.7462</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4814</v>
+        <v>1.5523</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0853</v>
+        <v>3.1939</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9235</v>
+        <v>-3.1722</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.7003</v>
+        <v>-2.8604</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2232</v>
+        <v>-0.3117</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3433</v>
+        <v>-1.0099</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4755</v>
+        <v>0.1209</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8678</v>
+        <v>-1.1308</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="W2" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6887</v>
+        <v>3.9996</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6274</v>
+        <v>5.8377</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9387</v>
+        <v>-1.8382</v>
       </c>
       <c r="G3" t="n">
-        <v>6.251</v>
+        <v>6.2746</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1386</v>
+        <v>1.0806</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1124</v>
+        <v>5.1939</v>
       </c>
       <c r="J3" t="n">
-        <v>8.2461</v>
+        <v>8.4809</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6392</v>
+        <v>2.7095</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6068</v>
+        <v>5.7715</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.995</v>
+        <v>-2.2064</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5006</v>
+        <v>-1.6289</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4944</v>
+        <v>-0.5775</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.5621</v>
+        <v>-1.3013</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.218</v>
+        <v>-0.3064</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3441</v>
+        <v>-0.9949</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1955</v>
+        <v>0.8125</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4458</v>
+        <v>4.8746</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2503</v>
+        <v>-4.0621</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0963</v>
+        <v>-0.149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7093</v>
+        <v>-1.9859</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8056</v>
+        <v>1.8368</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0413</v>
+        <v>2.9337</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6813</v>
+        <v>0.3799</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3599</v>
+        <v>2.5538</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1376</v>
+        <v>-3.0827</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9721</v>
+        <v>-2.3657</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1655</v>
+        <v>-0.717</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6002</v>
+        <v>0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4004</v>
+        <v>-0.3895</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8002</v>
+        <v>1.3632</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0323</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9452</v>
+        <v>-0.3396</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0871</v>
+        <v>-0.2314</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8597</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8597</v>
+        <v>2.67</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8067</v>
+        <v>0.7432</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2255</v>
+        <v>2.2942</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4188</v>
+        <v>-1.551</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0915</v>
+        <v>1.7621</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3014</v>
+        <v>0.3371</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3929</v>
+        <v>1.425</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7074</v>
+        <v>2.9344</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1418</v>
+        <v>0.9647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5656</v>
+        <v>1.9697</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6159</v>
+        <v>-1.1723</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4432</v>
+        <v>-0.6276</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8273</v>
+        <v>-0.5447</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2003</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2003</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2254</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5181</v>
+        <v>-0.3092</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.2319</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2598</v>
+        <v>-0.9416</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7097</v>
+        <v>0.4193</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3597</v>
+        <v>0.8067</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.65</v>
+        <v>-0.3874</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2098</v>
+        <v>0.0574</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9958</v>
+        <v>-1.3676</v>
       </c>
       <c r="I6" t="n">
-        <v>1.786</v>
+        <v>1.425</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6563</v>
+        <v>0.8178</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2472</v>
+        <v>0.1771</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4092</v>
+        <v>0.6407</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8661</v>
+        <v>-0.7604</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.243</v>
+        <v>-1.5447</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6231</v>
+        <v>0.7843</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4001</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4004</v>
+        <v>1.1684</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6004</v>
+        <v>-0.527</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4755</v>
+        <v>-0.0111</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1249</v>
+        <v>-0.5159</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5196</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.0594</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5742</v>
+        <v>0.2598</v>
       </c>
       <c r="E7" t="n">
-        <v>2.199</v>
+        <v>2.3405</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6248</v>
+        <v>-2.0807</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7398</v>
+        <v>-0.1999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3468</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3929</v>
+        <v>-0.8839</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8614</v>
+        <v>2.1223</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9397</v>
+        <v>1.7576</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9216</v>
+        <v>0.3647</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1216</v>
+        <v>-2.3222</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5929</v>
+        <v>-1.0736</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-1.2486</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3632</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2256</v>
+        <v>0.1539</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3223</v>
+        <v>0.6913</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09669999999999999</v>
+        <v>-0.5374</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3401</v>
+        <v>0.89</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1060,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3975</v>
+        <v>-0.8548</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3277</v>
+        <v>0.1274</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0698</v>
+        <v>-0.9822</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3132</v>
+        <v>-0.3255</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4847</v>
+        <v>1.4737</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7978</v>
+        <v>-1.7992</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3235</v>
+        <v>0.3942</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5995</v>
+        <v>1.6421</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.276</v>
+        <v>-1.248</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6367</v>
+        <v>-0.7197</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1149</v>
+        <v>-0.1684</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5218</v>
+        <v>-0.5513</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2844</v>
+        <v>-0.724</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4512</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.6521</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6074</v>
+        <v>-1.5913</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0551</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5523</v>
+        <v>-0.7904</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1247</v>
+        <v>-2.1137</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3755</v>
+        <v>0.3792</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5002</v>
+        <v>-2.493</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8307</v>
+        <v>-0.6994</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5614</v>
+        <v>1.6344</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.392</v>
+        <v>-2.3338</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.294</v>
+        <v>-1.4144</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1858</v>
+        <v>-1.2552</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5032</v>
+        <v>-0.4444</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0243</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4789</v>
+        <v>-0.5376</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8314</v>
+        <v>-2.7879</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8379</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9935</v>
+        <v>-1.9709</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.778</v>
+        <v>-0.765</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8892</v>
+        <v>-0.8687</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1112</v>
+        <v>0.1037</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8653</v>
+        <v>0.9744</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9034</v>
+        <v>0.9905</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0381</v>
+        <v>-0.0161</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6433</v>
+        <v>-1.7394</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7926</v>
+        <v>-1.8592</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1929</v>
+        <v>-0.2118</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0979</v>
+        <v>-0.0914</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2908</v>
+        <v>-0.1204</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2472</v>
+        <v>-3.0353</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4149</v>
+        <v>-1.9617</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-1.0736</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4127</v>
+        <v>-1.466</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2576</v>
+        <v>-2.2861</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8448</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1763</v>
+        <v>-0.1201</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3363</v>
+        <v>-0.2822</v>
       </c>
       <c r="L12" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2364</v>
+        <v>-1.346</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9213</v>
+        <v>-2.0039</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6849</v>
+        <v>0.6579</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7744</v>
+        <v>-0.5108</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8379</v>
+        <v>-0.5048</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0635</v>
+        <v>-0.006</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4511</v>
+        <v>1.792900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>16.9723</v>
+        <v>19.2902</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.521</v>
+        <v>-17.4974</v>
       </c>
       <c r="G13" t="n">
-        <v>4.390900000000001</v>
+        <v>4.2437</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.608</v>
+        <v>-3.8618</v>
       </c>
       <c r="I13" t="n">
-        <v>7.9988</v>
+        <v>8.105200000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>21.261</v>
+        <v>22.5844</v>
       </c>
       <c r="K13" t="n">
-        <v>10.8586</v>
+        <v>11.5259</v>
       </c>
       <c r="L13" t="n">
-        <v>10.4023</v>
+        <v>11.0585</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.87</v>
+        <v>-18.341</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.4667</v>
+        <v>-15.3876</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.403300000000001</v>
+        <v>-2.9532</v>
       </c>
       <c r="P13" t="n">
-        <v>9.99999999995449e-05</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.003</v>
+        <v>-9.736800000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>10.0027</v>
+        <v>9.736800000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.679399999999999</v>
+        <v>-5.2237</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2435</v>
+        <v>-0.7291</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.4358</v>
+        <v>-4.4946</v>
       </c>
       <c r="V13" t="n">
-        <v>2.7396</v>
+        <v>2.7732</v>
       </c>
       <c r="W13" t="n">
-        <v>6.9577</v>
+        <v>7.171599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.2181</v>
+        <v>-4.3985</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8422</v>
+        <v>3.7731</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5216</v>
+        <v>5.6396</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6794</v>
+        <v>-1.8665</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5856</v>
+        <v>3.3058</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6765</v>
+        <v>0.0118</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9091</v>
+        <v>3.294</v>
       </c>
       <c r="J14" t="n">
-        <v>4.0083</v>
+        <v>4.9438</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1266</v>
+        <v>1.7499</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8816</v>
+        <v>3.1939</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4227</v>
+        <v>-1.638</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4501</v>
+        <v>-1.7381</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0274</v>
+        <v>0.1001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4004</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4004</v>
+        <v>1.1684</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5563</v>
+        <v>0.9668</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6536999999999999</v>
+        <v>1.1426</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0974</v>
+        <v>-0.1758</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7</v>
+        <v>0.2795</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8597</v>
+        <v>1.5005</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5597</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0296</v>
+        <v>3.7485</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6276</v>
+        <v>5.1885</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.598</v>
+        <v>-1.44</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2482</v>
+        <v>2.6794</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0069</v>
+        <v>0.7765</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2552</v>
+        <v>1.9029</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7284</v>
+        <v>4.2385</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6431</v>
+        <v>2.3094</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0853</v>
+        <v>1.9292</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4802</v>
+        <v>-1.5591</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6501</v>
+        <v>-1.5329</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1699</v>
+        <v>-0.0262</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8002</v>
+        <v>1.3632</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3218</v>
+        <v>0.4033</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4402</v>
+        <v>0.06</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1184</v>
+        <v>0.3433</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2598</v>
+        <v>-0.6974</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4596</v>
+        <v>0.89</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1998</v>
+        <v>-1.5874</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.996</v>
+        <v>2.551</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9607</v>
+        <v>4.7107</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9646</v>
+        <v>-2.1598</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5087</v>
+        <v>-0.5216</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7623</v>
+        <v>0.7574</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2711</v>
+        <v>-1.279</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3851</v>
+        <v>2.5086</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8195</v>
+        <v>1.8679</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5656</v>
+        <v>0.6407</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8938</v>
+        <v>-3.0302</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0571</v>
+        <v>-1.1105</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8367</v>
+        <v>-1.9197</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8647</v>
+        <v>1.4388</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3758</v>
+        <v>0.9811</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4889</v>
+        <v>0.4578</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8398</v>
+        <v>0.8547</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7374</v>
+        <v>0.6158</v>
       </c>
       <c r="E17" t="n">
-        <v>5.062</v>
+        <v>0.6158</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3246</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.906</v>
+        <v>0.6158</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.598</v>
+        <v>0.6158</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.308</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1234</v>
+        <v>0.6158</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3235</v>
+        <v>0.6158</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7999000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.0294</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9215</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.1079</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3833</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.7591</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3758</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1795</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,28 +1813,28 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5998</v>
+        <v>0.3079</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5998</v>
+        <v>0.3079</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5998</v>
+        <v>0.3079</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5998</v>
+        <v>0.3079</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5998</v>
+        <v>0.3079</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5998</v>
+        <v>0.3079</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2999</v>
+        <v>-0.2515</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2999</v>
+        <v>3.1364</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-3.3879</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2999</v>
+        <v>-1.9573</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2999</v>
+        <v>-0.5824</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.3749</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2999</v>
+        <v>1.2057</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2999</v>
+        <v>0.3952</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8105</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-3.1631</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.9776</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-2.1855</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.4527</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.7028</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.2501</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2279</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6412</v>
+        <v>-0.4518</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7579</v>
+        <v>1.151</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3991</v>
+        <v>-1.6027</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0333</v>
+        <v>-0.0287</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3488</v>
+        <v>2.3672</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3821</v>
+        <v>-2.3958</v>
       </c>
       <c r="J20" t="n">
-        <v>2.325</v>
+        <v>2.4633</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9991</v>
+        <v>3.079</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6742</v>
+        <v>-0.6156</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3583</v>
+        <v>-2.492</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7079</v>
+        <v>-1.7802</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8124</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4335</v>
+        <v>0.635</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3789</v>
+        <v>0.3403</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0198</v>
+        <v>-0.0353</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0198</v>
+        <v>-0.0353</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. JIMENEZ BARRETO</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9353</v>
+        <v>-0.6845</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2512</v>
+        <v>2.9756</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-3.6601</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1011</v>
+        <v>-0.1551</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.426</v>
+        <v>2.8194</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3249</v>
+        <v>-2.9745</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1999</v>
+        <v>3.975</v>
       </c>
       <c r="K21" t="n">
-        <v>0.16</v>
+        <v>4.4852</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04</v>
+        <v>-0.5101</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3011</v>
+        <v>-4.1301</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.586</v>
+        <v>-1.6658</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2849</v>
+        <v>-2.4644</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4001</v>
+        <v>1.5579</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3746</v>
+        <v>0.8885</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4512</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0766</v>
+        <v>-0.111</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8597</v>
+        <v>-1.0284</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.0516</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8597</v>
+        <v>-0.9768</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>A. JIMENEZ BARRETO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9747</v>
+        <v>-0.7119</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6373</v>
+        <v>-0.0288</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6626</v>
+        <v>-0.6831</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2425</v>
+        <v>-0.182</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.9138</v>
+        <v>-0.4752</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3287</v>
+        <v>0.2932</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5485</v>
+        <v>0.2047</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5923</v>
+        <v>0.1642</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0438</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6939</v>
+        <v>-0.3868</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3214</v>
+        <v>-0.6394</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3725</v>
+        <v>0.2527</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1872</v>
+        <v>-0.0293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0888</v>
+        <v>-0.2335</v>
       </c>
       <c r="U22" t="n">
-        <v>0.276</v>
+        <v>0.2042</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6802</v>
+        <v>-0.89</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6802</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4915</v>
+        <v>-0.9431</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3688</v>
+        <v>-1.2881</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8603</v>
+        <v>0.345</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2974</v>
+        <v>-3.2388</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6603</v>
+        <v>-2.8967</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9577</v>
+        <v>-0.3421</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6537</v>
+        <v>-1.4191</v>
       </c>
       <c r="K23" t="n">
-        <v>4.246</v>
+        <v>-1.5085</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5923</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.9511</v>
+        <v>-1.8196</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5857</v>
+        <v>-1.3881</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.3654</v>
+        <v>-0.4315</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6005</v>
+        <v>1.3632</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2461</v>
+        <v>0.2704</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.1311</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5498</v>
+        <v>0.1393</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0401</v>
+        <v>0.6621</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0803</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9598</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1842</v>
+        <v>-4.1293</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6257</v>
+        <v>-2.3186</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5585</v>
+        <v>-1.8108</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6242</v>
+        <v>-4.6548</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3799</v>
+        <v>-0.39</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.2444</v>
+        <v>-4.2648</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8522</v>
+        <v>-1.7759</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1418</v>
+        <v>0.1771</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.994</v>
+        <v>-1.953</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.772</v>
+        <v>-2.8789</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5671</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2503</v>
+        <v>-2.3118</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0002</v>
+        <v>0.1128</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7735</v>
+        <v>-0.5427</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7732</v>
+        <v>0.6555</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7292</v>
+        <v>-4.6435</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.163</v>
+        <v>-2.5928</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5662</v>
+        <v>-2.0507</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4111</v>
+        <v>-0.4142</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5849</v>
+        <v>0.5501</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9961</v>
+        <v>-0.9643</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9472</v>
+        <v>1.0725</v>
       </c>
       <c r="K25" t="n">
-        <v>1.6995</v>
+        <v>1.7447</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7523</v>
+        <v>-0.6722</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3583</v>
+        <v>-1.4867</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1146</v>
+        <v>-1.1947</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2438</v>
+        <v>-0.292</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3175</v>
+        <v>-0.282</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.709</v>
+        <v>-0.3812</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3915</v>
+        <v>0.0992</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.4512</v>
+        <v>-0.819300000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>15.5211</v>
+        <v>17.4972</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.9721</v>
+        <v>-18.3166</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.3908</v>
+        <v>-4.2436</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6079</v>
+        <v>3.861800000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.9989</v>
+        <v>-8.1053</v>
       </c>
       <c r="J26" t="n">
-        <v>16.87</v>
+        <v>18.3408</v>
       </c>
       <c r="K26" t="n">
-        <v>14.4665</v>
+        <v>15.3878</v>
       </c>
       <c r="L26" t="n">
-        <v>2.4034</v>
+        <v>2.9533</v>
       </c>
       <c r="M26" t="n">
-        <v>-21.2608</v>
+        <v>-22.5845</v>
       </c>
       <c r="N26" t="n">
-        <v>-10.8585</v>
+        <v>-11.526</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.4023</v>
+        <v>-11.0585</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-10.0029</v>
+        <v>-9.7369</v>
       </c>
       <c r="R26" t="n">
-        <v>10.0028</v>
+        <v>9.736800000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>5.6795</v>
+        <v>6.1973</v>
       </c>
       <c r="T26" t="n">
-        <v>4.435700000000001</v>
+        <v>4.4947</v>
       </c>
       <c r="U26" t="n">
-        <v>1.2437</v>
+        <v>1.7027</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.7396</v>
+        <v>-2.7733</v>
       </c>
       <c r="W26" t="n">
-        <v>4.2182</v>
+        <v>4.398400000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.957699999999999</v>
+        <v>-7.1717</v>
       </c>
     </row>
   </sheetData>
